--- a/diseases/d242/2015-2019.xlsx
+++ b/diseases/d242/2015-2019.xlsx
@@ -45048,7 +45048,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -46630,7 +46630,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -47033,7 +47033,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -47436,7 +47436,7 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -47839,7 +47839,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -48242,7 +48242,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -48645,7 +48645,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -49048,7 +49048,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -49451,7 +49451,7 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -49854,7 +49854,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -50257,7 +50257,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -50660,7 +50660,7 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN254" t="b">

--- a/diseases/d242/2015-2019.xlsx
+++ b/diseases/d242/2015-2019.xlsx
@@ -45048,7 +45048,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -46630,7 +46630,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -47033,7 +47033,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -47436,7 +47436,7 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -47839,7 +47839,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -48242,7 +48242,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -48645,7 +48645,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -49048,7 +49048,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -49451,7 +49451,7 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -49854,7 +49854,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -50257,7 +50257,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -50660,7 +50660,7 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN254" t="b">

--- a/diseases/d242/2015-2019.xlsx
+++ b/diseases/d242/2015-2019.xlsx
@@ -3792,11 +3792,6 @@
       <c r="R23" t="n">
         <v>0.04854493829210169</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>SER_SI_ECDC_LGV_ANNUAL</t>
@@ -3814,12 +3809,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -3829,11 +3819,6 @@
       </c>
       <c r="AT23" t="n">
         <v>1</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3899,17 +3884,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3934,48 +3919,26 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2015-01-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>80</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.7059217703670895</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3983,64 +3946,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN24" t="b">
-        <v>1</v>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4048,27 +3953,17 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT24" t="n">
         <v>1</v>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -4076,7 +3971,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -4096,7 +3991,7 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -4138,12 +4033,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4177,17 +4072,17 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7059217703670895</v>
+        <v>0</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4207,7 +4102,7 @@
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT25" t="n">
@@ -4220,7 +4115,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -4240,7 +4135,7 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -4282,12 +4177,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4321,17 +4216,17 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.3703018662834264</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4351,7 +4246,7 @@
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT26" t="n">
@@ -4364,7 +4259,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -4384,7 +4279,7 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -4426,12 +4321,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4465,17 +4360,17 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O27" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3703018662834264</v>
+        <v>0.7681294703171205</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4495,7 +4390,7 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT27" t="n">
@@ -4508,7 +4403,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -4528,7 +4423,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -4570,12 +4465,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4609,17 +4504,17 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.7681294703171205</v>
+        <v>0</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4639,7 +4534,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -4652,7 +4547,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -4672,7 +4567,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -4714,12 +4609,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4753,17 +4648,17 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.5306768562899897</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_ES_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4783,7 +4678,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_ES_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -4796,7 +4691,7 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -4816,7 +4711,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -4858,12 +4753,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4897,17 +4792,17 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>248</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>248</v>
+        <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>0.5306768562899897</v>
+        <v>0.1455744723516774</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4927,7 +4822,7 @@
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT30" t="n">
@@ -4935,42 +4830,42 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -5002,12 +4897,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5041,17 +4936,17 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>596</v>
       </c>
       <c r="O31" t="n">
-        <v>8</v>
+        <v>596</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1455744723516774</v>
+        <v>0.9156994840532739</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -5071,7 +4966,7 @@
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT31" t="n">
@@ -5079,42 +4974,42 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5146,12 +5041,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5185,17 +5080,17 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>596</v>
+        <v>919</v>
       </c>
       <c r="O32" t="n">
-        <v>596</v>
+        <v>919</v>
       </c>
       <c r="R32" t="n">
-        <v>0.9156994840532739</v>
+        <v>1.394677745820755</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5215,7 +5110,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -5228,7 +5123,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -5248,7 +5143,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -5290,12 +5185,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5329,17 +5224,17 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>919</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>919</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.394677745820755</v>
+        <v>0</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5359,7 +5254,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -5372,7 +5267,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -5392,7 +5287,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -5434,12 +5329,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5473,17 +5368,17 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>0.1427037799784966</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5503,7 +5398,7 @@
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT34" t="n">
@@ -5516,7 +5411,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -5536,7 +5431,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -5578,12 +5473,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5617,17 +5512,17 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="O35" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="R35" t="n">
-        <v>0.1427037799784966</v>
+        <v>1.051855862928876</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5647,7 +5542,7 @@
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT35" t="n">
@@ -5655,42 +5550,42 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -5722,12 +5617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5761,17 +5656,17 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.051855862928876</v>
+        <v>0</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_IS_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5791,7 +5686,7 @@
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_IS_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT36" t="n">
@@ -5799,42 +5694,42 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5866,12 +5761,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5905,17 +5800,17 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>0.03968378144107767</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5935,7 +5830,7 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT37" t="n">
@@ -5943,42 +5838,42 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6010,12 +5905,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6049,17 +5944,17 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.03968378144107767</v>
+        <v>0</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -6079,7 +5974,7 @@
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT38" t="n">
@@ -6092,7 +5987,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -6112,7 +6007,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -6154,12 +6049,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6203,7 +6098,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6223,7 +6118,7 @@
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT39" t="n">
@@ -6236,7 +6131,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -6256,7 +6151,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -6298,12 +6193,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6347,7 +6242,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6367,7 +6262,7 @@
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT40" t="n">
@@ -6380,7 +6275,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -6400,7 +6295,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -6442,12 +6337,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6491,7 +6386,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6511,7 +6406,7 @@
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT41" t="n">
@@ -6524,7 +6419,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -6544,7 +6439,7 @@
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -6586,12 +6481,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6625,17 +6520,17 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.424030059705221</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6655,7 +6550,7 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT42" t="n">
@@ -6668,7 +6563,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -6688,7 +6583,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -6730,12 +6625,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6769,17 +6664,17 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.424030059705221</v>
+        <v>0</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6799,7 +6694,7 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT43" t="n">
@@ -6812,7 +6707,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -6832,7 +6727,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -6874,12 +6769,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6913,17 +6808,17 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.04832611856600555</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_PT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6943,7 +6838,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_PT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -6956,7 +6851,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -6976,7 +6871,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -7018,12 +6913,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7057,17 +6952,17 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O45" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="R45" t="n">
-        <v>0.04832611856600555</v>
+        <v>0.2015462629291928</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -7087,7 +6982,7 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT45" t="n">
@@ -7095,42 +6990,42 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -7162,12 +7057,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7201,17 +7096,17 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0.2015462629291928</v>
+        <v>0.04851135626594508</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7231,7 +7126,7 @@
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT46" t="n">
@@ -7239,42 +7134,42 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7306,12 +7201,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7336,31 +7231,26 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2016-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="R47" t="n">
-        <v>0.04851135626594508</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0.7735188970007288</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7375,27 +7265,17 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT47" t="n">
         <v>1</v>
       </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -7403,7 +7283,7 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -7423,7 +7303,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -7460,17 +7340,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7495,48 +7375,26 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2016-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7544,64 +7402,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG48" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN48" t="b">
-        <v>1</v>
-      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -7609,27 +7409,17 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT48" t="n">
         <v>1</v>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -7637,7 +7427,7 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -7657,7 +7447,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -7699,12 +7489,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7738,17 +7528,17 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="O49" t="n">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="R49" t="n">
-        <v>0.7735188970007288</v>
+        <v>0.3699718864055396</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7768,7 +7558,7 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT49" t="n">
@@ -7781,7 +7571,7 @@
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -7801,7 +7591,7 @@
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -7843,12 +7633,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7882,17 +7672,17 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>0.7111674802885189</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7912,7 +7702,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -7925,7 +7715,7 @@
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -7945,7 +7735,7 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -7987,12 +7777,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8026,17 +7816,17 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.3699718864055396</v>
+        <v>0</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -8056,7 +7846,7 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -8069,7 +7859,7 @@
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -8089,7 +7879,7 @@
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -8131,12 +7921,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8170,17 +7960,17 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>41</v>
+        <v>328</v>
       </c>
       <c r="O52" t="n">
-        <v>41</v>
+        <v>328</v>
       </c>
       <c r="R52" t="n">
-        <v>0.7111674802885189</v>
+        <v>0.699828950496287</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_ES_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -8200,7 +7990,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_ES_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -8213,7 +8003,7 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -8233,7 +8023,7 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -8275,12 +8065,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8314,17 +8104,17 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>0.1089246306910397</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -8344,7 +8134,7 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -8352,42 +8142,42 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -8419,12 +8209,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8458,17 +8248,17 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>328</v>
+        <v>457</v>
       </c>
       <c r="O54" t="n">
-        <v>328</v>
+        <v>457</v>
       </c>
       <c r="R54" t="n">
-        <v>0.699828950496287</v>
+        <v>0.700010060538463</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8488,7 +8278,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -8501,7 +8291,7 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -8521,7 +8311,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -8563,12 +8353,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8602,17 +8392,17 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>641</v>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>641</v>
       </c>
       <c r="R55" t="n">
-        <v>0.1089246306910397</v>
+        <v>0.9660238267893055</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8632,7 +8422,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -8640,42 +8430,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8497,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8746,17 +8536,17 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>457</v>
+        <v>2</v>
       </c>
       <c r="O56" t="n">
-        <v>457</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>0.700010060538463</v>
+        <v>0.04902922141596391</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8776,7 +8566,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -8789,7 +8579,7 @@
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -8809,7 +8599,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -8851,12 +8641,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8890,17 +8680,17 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>641</v>
+        <v>22</v>
       </c>
       <c r="O57" t="n">
-        <v>641</v>
+        <v>22</v>
       </c>
       <c r="R57" t="n">
-        <v>0.9660238267893055</v>
+        <v>0.2248200404992865</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8920,7 +8710,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -8933,7 +8723,7 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -8953,7 +8743,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -8995,12 +8785,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9034,17 +8824,17 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="O58" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R58" t="n">
-        <v>0.04902922141596391</v>
+        <v>0.3949890031943176</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -9064,7 +8854,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -9072,42 +8862,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -9139,12 +8929,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9178,17 +8968,17 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.2248200404992865</v>
+        <v>0</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IS_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -9208,7 +8998,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IS_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -9216,42 +9006,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9283,12 +9073,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9322,17 +9112,17 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R60" t="n">
-        <v>0.3949890031943176</v>
+        <v>0.03311789151366946</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -9352,7 +9142,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -9360,42 +9150,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9427,12 +9217,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9476,7 +9266,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_LGV_ANNUAL</t>
+          <t>SER_LT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9496,7 +9286,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_LGV_ANNUAL</t>
+          <t>SER_LT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -9504,42 +9294,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9571,12 +9361,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9610,17 +9400,17 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.03311789151366946</v>
+        <v>0</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9640,7 +9430,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -9653,7 +9443,7 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
@@ -9673,7 +9463,7 @@
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -9715,12 +9505,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9764,7 +9554,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9784,7 +9574,7 @@
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT63" t="n">
@@ -9797,7 +9587,7 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
@@ -9817,7 +9607,7 @@
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -9859,12 +9649,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9908,7 +9698,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9928,7 +9718,7 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -9941,7 +9731,7 @@
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -9961,7 +9751,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -10003,12 +9793,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10042,17 +9832,17 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.576633938518207</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -10072,7 +9862,7 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -10085,7 +9875,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -10105,7 +9895,7 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -10147,12 +9937,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10196,7 +9986,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -10216,7 +10006,7 @@
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT66" t="n">
@@ -10229,7 +10019,7 @@
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -10249,7 +10039,7 @@
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
@@ -10291,12 +10081,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10330,17 +10120,17 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>273</v>
+        <v>31</v>
       </c>
       <c r="O67" t="n">
-        <v>273</v>
+        <v>31</v>
       </c>
       <c r="R67" t="n">
-        <v>1.576633938518207</v>
+        <v>0.3000722883822464</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_PT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -10360,7 +10150,7 @@
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_PT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT67" t="n">
@@ -10373,7 +10163,7 @@
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -10393,7 +10183,7 @@
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
@@ -10435,12 +10225,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10484,7 +10274,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -10504,7 +10294,7 @@
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT68" t="n">
@@ -10512,42 +10302,42 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -10579,12 +10369,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10618,17 +10408,17 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="O69" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>0.3000722883822464</v>
+        <v>0.09697392855930684</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -10648,7 +10438,7 @@
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT69" t="n">
@@ -10661,7 +10451,7 @@
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
@@ -10681,7 +10471,7 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -10723,12 +10513,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10753,26 +10543,26 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>0.7612477638346937</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -10792,7 +10582,7 @@
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT70" t="n">
@@ -10800,42 +10590,42 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -10867,12 +10657,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10897,31 +10687,26 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.09697392855930684</v>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10936,27 +10721,17 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT71" t="n">
         <v>1</v>
       </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV71" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -10964,7 +10739,7 @@
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
@@ -10984,7 +10759,7 @@
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -11021,17 +10796,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11056,48 +10831,26 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="O72" t="n">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.2369907034234824</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -11105,64 +10858,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN72" t="b">
-        <v>1</v>
-      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -11170,27 +10865,17 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT72" t="n">
         <v>1</v>
       </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV72" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -11198,7 +10883,7 @@
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -11218,7 +10903,7 @@
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
@@ -11260,12 +10945,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11299,17 +10984,17 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="O73" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="R73" t="n">
-        <v>0.7612477638346937</v>
+        <v>1.08736465869824</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -11329,7 +11014,7 @@
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT73" t="n">
@@ -11342,7 +11027,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -11362,7 +11047,7 @@
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -11404,12 +11089,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11453,7 +11138,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -11473,7 +11158,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -11486,7 +11171,7 @@
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -11506,7 +11191,7 @@
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -11548,12 +11233,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11587,17 +11272,17 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>25</v>
+        <v>286</v>
       </c>
       <c r="O75" t="n">
-        <v>25</v>
+        <v>286</v>
       </c>
       <c r="R75" t="n">
-        <v>0.2369907034234824</v>
+        <v>0.6073112502646635</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_ES_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -11617,7 +11302,7 @@
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_ES_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT75" t="n">
@@ -11630,7 +11315,7 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -11650,7 +11335,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -11692,12 +11377,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11731,17 +11416,17 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="O76" t="n">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="R76" t="n">
-        <v>1.08736465869824</v>
+        <v>0.3082090669124604</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -11761,7 +11446,7 @@
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT76" t="n">
@@ -11769,42 +11454,42 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -11836,12 +11521,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11875,17 +11560,17 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>694</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>694</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.059225955370491</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -11905,7 +11590,7 @@
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT77" t="n">
@@ -11918,7 +11603,7 @@
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
@@ -11938,7 +11623,7 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -11980,12 +11665,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12019,17 +11704,17 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>286</v>
+        <v>805</v>
       </c>
       <c r="O78" t="n">
-        <v>286</v>
+        <v>805</v>
       </c>
       <c r="R78" t="n">
-        <v>0.6073112502646635</v>
+        <v>1.205947794445075</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -12049,7 +11734,7 @@
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT78" t="n">
@@ -12062,7 +11747,7 @@
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -12082,7 +11767,7 @@
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -12124,12 +11809,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12163,17 +11848,17 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0.3082090669124604</v>
+        <v>0</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -12193,7 +11878,7 @@
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT79" t="n">
@@ -12201,42 +11886,42 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12268,12 +11953,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12307,17 +11992,17 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>694</v>
+        <v>41</v>
       </c>
       <c r="O80" t="n">
-        <v>694</v>
+        <v>41</v>
       </c>
       <c r="R80" t="n">
-        <v>1.059225955370491</v>
+        <v>0.4194633661924906</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -12337,7 +12022,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT80" t="n">
@@ -12350,7 +12035,7 @@
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -12370,7 +12055,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -12412,12 +12097,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12451,17 +12136,17 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>805</v>
+        <v>29</v>
       </c>
       <c r="O81" t="n">
-        <v>805</v>
+        <v>29</v>
       </c>
       <c r="R81" t="n">
-        <v>1.205947794445075</v>
+        <v>0.595170234592505</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -12481,7 +12166,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT81" t="n">
@@ -12489,42 +12174,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -12556,12 +12241,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12605,7 +12290,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IS_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12625,7 +12310,7 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IS_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT82" t="n">
@@ -12633,42 +12318,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12700,12 +12385,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12739,17 +12424,17 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="O83" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="R83" t="n">
-        <v>0.4194633661924906</v>
+        <v>0.03483887109217049</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12769,7 +12454,7 @@
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT83" t="n">
@@ -12782,7 +12467,7 @@
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
@@ -12802,7 +12487,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -12844,12 +12529,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12883,17 +12568,17 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.595170234592505</v>
+        <v>0</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12913,7 +12598,7 @@
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT84" t="n">
@@ -12921,42 +12606,42 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12988,12 +12673,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -13037,7 +12722,7 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -13057,7 +12742,7 @@
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT85" t="n">
@@ -13065,42 +12750,42 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -13132,12 +12817,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13171,17 +12856,17 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.03483887109217049</v>
+        <v>0</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -13201,7 +12886,7 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT86" t="n">
@@ -13214,7 +12899,7 @@
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -13234,7 +12919,7 @@
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -13276,12 +12961,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13325,7 +13010,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -13345,7 +13030,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -13358,7 +13043,7 @@
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
@@ -13378,7 +13063,7 @@
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
@@ -13420,12 +13105,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13459,17 +13144,17 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.348925031597134</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -13489,7 +13174,7 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT88" t="n">
@@ -13502,7 +13187,7 @@
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
@@ -13522,7 +13207,7 @@
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
@@ -13564,12 +13249,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13613,7 +13298,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13633,7 +13318,7 @@
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -13646,7 +13331,7 @@
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
@@ -13666,7 +13351,7 @@
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
@@ -13708,12 +13393,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13747,17 +13432,17 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>0.4164506530672607</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_PT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13777,7 +13462,7 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_PT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT90" t="n">
@@ -13790,7 +13475,7 @@
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
@@ -13810,7 +13495,7 @@
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
@@ -13852,12 +13537,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13891,17 +13576,17 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>235</v>
+        <v>6</v>
       </c>
       <c r="O91" t="n">
-        <v>235</v>
+        <v>6</v>
       </c>
       <c r="R91" t="n">
-        <v>1.348925031597134</v>
+        <v>0.2899278345459162</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -13921,7 +13606,7 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT91" t="n">
@@ -13934,7 +13619,7 @@
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
@@ -13954,7 +13639,7 @@
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
@@ -13996,12 +13681,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -14026,26 +13711,26 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.261899055385881</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -14065,7 +13750,7 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT92" t="n">
@@ -14078,7 +13763,7 @@
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
@@ -14098,7 +13783,7 @@
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
@@ -14140,12 +13825,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -14170,26 +13855,26 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0.4164506530672607</v>
+        <v>0</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -14209,7 +13894,7 @@
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT93" t="n">
@@ -14222,7 +13907,7 @@
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
@@ -14242,7 +13927,7 @@
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
@@ -14284,12 +13969,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14314,31 +13999,26 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O94" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="R94" t="n">
-        <v>0.2899278345459162</v>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0.1326401307452717</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -14353,27 +14033,17 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT94" t="n">
         <v>1</v>
       </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV94" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -14381,7 +14051,7 @@
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
@@ -14401,7 +14071,7 @@
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
@@ -14438,17 +14108,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -14473,48 +14143,26 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="O95" t="n">
-        <v>6</v>
+        <v>70</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1.203862299822422</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -14522,64 +14170,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG95" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN95" t="b">
-        <v>1</v>
-      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -14587,27 +14177,17 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT95" t="n">
         <v>1</v>
       </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV95" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -14615,7 +14195,7 @@
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
@@ -14635,7 +14215,7 @@
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
@@ -14677,12 +14257,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -14716,17 +14296,17 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>1.261899055385881</v>
+        <v>0</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -14746,7 +14326,7 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT96" t="n">
@@ -14759,7 +14339,7 @@
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
@@ -14779,7 +14359,7 @@
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
@@ -14821,12 +14401,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -14860,17 +14440,17 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>417</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>417</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>0.879095507275949</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_ES_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -14890,7 +14470,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_ES_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -14903,7 +14483,7 @@
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
@@ -14923,7 +14503,7 @@
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
@@ -14965,12 +14545,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -15004,17 +14584,17 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O98" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R98" t="n">
-        <v>0.1326401307452717</v>
+        <v>0.1448813684190129</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -15034,7 +14614,7 @@
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT98" t="n">
@@ -15042,42 +14622,42 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15109,12 +14689,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -15148,17 +14728,17 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>70</v>
+        <v>721</v>
       </c>
       <c r="O99" t="n">
-        <v>70</v>
+        <v>721</v>
       </c>
       <c r="R99" t="n">
-        <v>1.203862299822422</v>
+        <v>1.096920636453131</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -15178,7 +14758,7 @@
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -15191,7 +14771,7 @@
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
@@ -15211,7 +14791,7 @@
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
@@ -15253,12 +14833,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -15292,17 +14872,17 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1202</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>1202</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.791063688883714</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -15322,7 +14902,7 @@
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT100" t="n">
@@ -15335,7 +14915,7 @@
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
@@ -15355,7 +14935,7 @@
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
@@ -15397,12 +14977,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -15436,17 +15016,17 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>417</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>417</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0.879095507275949</v>
+        <v>0</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -15466,7 +15046,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -15479,7 +15059,7 @@
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
@@ -15499,7 +15079,7 @@
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
@@ -15541,12 +15121,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15580,17 +15160,17 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="O102" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="R102" t="n">
-        <v>0.1448813684190129</v>
+        <v>0.501517525504341</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -15610,7 +15190,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -15618,42 +15198,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -15685,12 +15265,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -15724,17 +15304,17 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>721</v>
+        <v>39</v>
       </c>
       <c r="O103" t="n">
-        <v>721</v>
+        <v>39</v>
       </c>
       <c r="R103" t="n">
-        <v>1.096920636453131</v>
+        <v>0.790515276099622</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -15754,7 +15334,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -15762,42 +15342,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -15829,12 +15409,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -15868,17 +15448,17 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>1202</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>1202</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>1.791063688883714</v>
+        <v>0</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_IS_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -15898,7 +15478,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_IS_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT104" t="n">
@@ -15906,42 +15486,42 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -15973,12 +15553,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -16012,17 +15592,17 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>0.01330447681009735</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -16042,7 +15622,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -16055,7 +15635,7 @@
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
@@ -16075,7 +15655,7 @@
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
@@ -16117,12 +15697,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -16156,17 +15736,17 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0.501517525504341</v>
+        <v>0</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_LT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -16186,7 +15766,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_LT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -16199,7 +15779,7 @@
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
@@ -16219,7 +15799,7 @@
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
@@ -16261,12 +15841,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -16300,17 +15880,17 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>0.790515276099622</v>
+        <v>0</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -16330,7 +15910,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -16338,42 +15918,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -16405,12 +15985,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -16454,7 +16034,7 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -16474,7 +16054,7 @@
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT108" t="n">
@@ -16482,42 +16062,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -16549,12 +16129,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -16588,17 +16168,17 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O109" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R109" t="n">
-        <v>0.01330447681009735</v>
+        <v>1.190439579735147</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -16618,7 +16198,7 @@
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT109" t="n">
@@ -16631,7 +16211,7 @@
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
@@ -16651,7 +16231,7 @@
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
@@ -16693,12 +16273,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -16732,17 +16312,17 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>353</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>353</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.01282884733845</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -16762,7 +16342,7 @@
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT110" t="n">
@@ -16775,7 +16355,7 @@
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
@@ -16795,7 +16375,7 @@
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
@@ -16837,12 +16417,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -16876,22 +16456,22 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>0.01869952122680827</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -16906,7 +16486,7 @@
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT111" t="n">
@@ -16914,42 +16494,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16981,12 +16561,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -17020,17 +16600,17 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>0.005232056827880594</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -17050,7 +16630,7 @@
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT112" t="n">
@@ -17063,7 +16643,7 @@
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
@@ -17083,7 +16663,7 @@
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
@@ -17125,12 +16705,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -17164,17 +16744,17 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="O113" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="R113" t="n">
-        <v>1.190439579735147</v>
+        <v>0.483408782164691</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_PT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -17194,7 +16774,7 @@
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_PT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -17207,7 +16787,7 @@
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
@@ -17227,7 +16807,7 @@
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
@@ -17269,12 +16849,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -17308,17 +16888,17 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>353</v>
+        <v>14</v>
       </c>
       <c r="O114" t="n">
-        <v>353</v>
+        <v>14</v>
       </c>
       <c r="R114" t="n">
-        <v>2.01282884733845</v>
+        <v>0.6719657566250424</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -17338,7 +16918,7 @@
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT114" t="n">
@@ -17351,7 +16931,7 @@
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
@@ -17371,7 +16951,7 @@
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
@@ -17443,22 +17023,22 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R115" t="n">
-        <v>0.01869952122680827</v>
+        <v>0.03739904245361654</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -17557,12 +17137,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -17587,31 +17167,31 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2019-03</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>0.005232056827880594</v>
+        <v>0</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -17626,7 +17206,7 @@
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -17634,42 +17214,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17701,12 +17281,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -17731,31 +17311,31 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="O117" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="R117" t="n">
-        <v>0.483408782164691</v>
+        <v>0.07479808490723308</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_LGV_ANNUAL</t>
+          <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -17770,7 +17350,7 @@
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_LGV_ANNUAL</t>
+          <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -17778,42 +17358,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17845,12 +17425,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -17875,36 +17455,31 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O118" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R118" t="n">
-        <v>0.6719657566250424</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0.0560985636804248</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -17914,65 +17489,55 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT118" t="n">
         <v>1</v>
       </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17999,17 +17564,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -18034,112 +17599,32 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2019-06</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN119" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -18148,65 +17633,55 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_NO_FHI_910_MONTHLY</t>
         </is>
       </c>
       <c r="AT119" t="n">
         <v>1</v>
       </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18268,22 +17743,22 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>0.03739904245361654</v>
+        <v>0.01869952122680827</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -18412,22 +17887,22 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2019-08</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>0.01869952122680827</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -18556,22 +18031,22 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2019-09</t>
         </is>
       </c>
       <c r="N122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R122" t="n">
-        <v>0.07479808490723308</v>
+        <v>0.09349760613404134</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -18700,12 +18175,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="N123" t="n">
@@ -18844,22 +18319,22 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2019-06</t>
+          <t>2019-11</t>
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>0.09349760613404134</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -18988,22 +18463,22 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2019-12</t>
         </is>
       </c>
       <c r="N125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R125" t="n">
-        <v>0.01869952122680827</v>
+        <v>0.03739904245361654</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -19069,726 +18544,6 @@
         </is>
       </c>
       <c r="BC125" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>2019-08-01</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>2019-08</t>
-        </is>
-      </c>
-      <c r="N126" t="n">
-        <v>1</v>
-      </c>
-      <c r="O126" t="n">
-        <v>1</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0.01869952122680827</v>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP126" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV126" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW126" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA126" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB126" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC126" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>2019-09-01</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>2019-09</t>
-        </is>
-      </c>
-      <c r="N127" t="n">
-        <v>5</v>
-      </c>
-      <c r="O127" t="n">
-        <v>5</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.09349760613404134</v>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP127" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT127" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV127" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW127" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA127" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB127" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC127" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>2019-10-01</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>2019-10</t>
-        </is>
-      </c>
-      <c r="N128" t="n">
-        <v>3</v>
-      </c>
-      <c r="O128" t="n">
-        <v>3</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0.0560985636804248</v>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP128" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT128" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV128" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW128" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA128" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB128" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC128" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>2019-11-01</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>2019-11</t>
-        </is>
-      </c>
-      <c r="N129" t="n">
-        <v>5</v>
-      </c>
-      <c r="O129" t="n">
-        <v>5</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0.09349760613404134</v>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP129" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV129" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW129" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA129" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB129" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC129" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>2019-12-01</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>2019-12</t>
-        </is>
-      </c>
-      <c r="N130" t="n">
-        <v>2</v>
-      </c>
-      <c r="O130" t="n">
-        <v>2</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0.03739904245361654</v>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP130" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT130" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV130" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW130" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA130" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB130" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC130" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -19920,7 +18675,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
@@ -19940,7 +18695,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -19950,7 +18705,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
